--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>24/10 17:45</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>200</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,10 +548,8 @@
           <t>24/10 17:15</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>225</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -595,10 +591,8 @@
           <t>25/10 17:15</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>200</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -640,10 +634,8 @@
           <t>24/10 17:45</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>175</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -685,10 +677,8 @@
           <t>24/10 16:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>175</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -730,10 +720,8 @@
           <t>23/10 22:45</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>200</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -775,10 +763,8 @@
           <t>23/10 23:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>200</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -820,10 +806,8 @@
           <t>23/10 23:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>200</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -865,10 +849,8 @@
           <t>23/10 23:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>200</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -910,10 +892,8 @@
           <t>24/10 17:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>175</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -955,10 +935,8 @@
           <t>23/10 23:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>200</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1000,10 +978,8 @@
           <t>24/10 17:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>175</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1045,10 +1021,8 @@
           <t>24/10 01:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>200</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1090,10 +1064,8 @@
           <t>23/10 17:30</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>175</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1135,10 +1107,8 @@
           <t>24/10 01:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>200</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1180,10 +1150,8 @@
           <t>24/10 17:30</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>175</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1225,10 +1193,8 @@
           <t>24/10 01:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>175</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1270,10 +1236,8 @@
           <t>24/10 00:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>175</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1315,10 +1279,8 @@
           <t>24/10 00:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>175</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1360,10 +1322,8 @@
           <t>24/10 00:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>175</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1405,10 +1365,8 @@
           <t>24/10 16:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>150</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1450,10 +1408,8 @@
           <t>23/10 23:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>175</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1495,10 +1451,8 @@
           <t>23/10 17:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>150</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1540,10 +1494,8 @@
           <t>24/10 17:15</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>140</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1585,10 +1537,8 @@
           <t>24/10 15:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>140</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1602,6 +1552,51 @@
       </c>
       <c r="I26" s="2" t="n">
         <v>45953.07066555556</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Augsburger</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Augsburger Panther – IngolstadtAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>23/10 17:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+162%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45953.12871210491</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,23 +1580,111 @@
           <t>23/10 17:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" t="n">
+        <v>200</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+162%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45953.12871210648</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Spusu Vien</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Spusu Vienna Capitals – Pioneers VorarlbergICE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>25/10 17:15</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>200.00</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>+162%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>45953.12871210491</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+181%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45953.18479488594</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Black Wing</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Black Wings Linz – Graz 99ersAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>24/10 17:15</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+124%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45953.18479488594</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,10 +1623,8 @@
           <t>25/10 17:15</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>200</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1639,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45953.18479488594</v>
+        <v>45953.18479488426</v>
       </c>
     </row>
     <row r="29">
@@ -1668,10 +1666,8 @@
           <t>24/10 17:15</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>150</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1684,7 +1680,52 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45953.18479488594</v>
+        <v>45953.18479488426</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Banska Bys</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Banska Bystrica – HK PopradExtraliga</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>24/10 15:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+110%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45953.22331445153</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>24/10 15:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>140</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,52 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45953.22331445153</v>
+        <v>45953.22331445602</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Ambri P</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HC Ambri Piotta – Genève-ServetteNational League A</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>24/10 17:45</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+135%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45953.27310972373</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,23 +1752,111 @@
           <t>24/10 17:45</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" t="n">
+        <v>150</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+135%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45953.27310972222</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Djurgaarde</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Djurgaardens IF – Orebro HKSHL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>23/10 17:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+165%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45953.30731126175</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lowen Fran</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Lowen Frankfurt – Fischtown PinguinsDEL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>24/10 17:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>150.00</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>+135%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>45953.27310972373</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+117%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45953.30731126175</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -1795,10 +1795,8 @@
           <t>23/10 17:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>175</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45953.30731126175</v>
+        <v>45953.30731126157</v>
       </c>
     </row>
     <row r="33">
@@ -1840,10 +1838,8 @@
           <t>24/10 17:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>150</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1856,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45953.30731126175</v>
+        <v>45953.30731126157</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1855,6 +1855,51 @@
         <v>45953.30731126157</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Rogle BK –</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Rogle BK – Malmo RedhawksSHL</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>23/10 17:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+110%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45953.39204895535</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,23 +1881,66 @@
           <t>23/10 17:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="n">
+        <v>140</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+110%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45953.39204895833</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | EHC Munich</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EHC Munich – BerlinDEL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>23/10 17:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>1,50%</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>+110%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>45953.39204895535</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+108%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45953.43331277713</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1924,10 +1924,8 @@
           <t>23/10 17:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>140</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1940,7 +1938,52 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45953.43331277713</v>
+        <v>45953.43331277778</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Dresdner –</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Dresdner – Straubing TigersAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>24/10 17:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+163%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45953.4715040279</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,10 +1967,8 @@
           <t>24/10 17:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>200</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,52 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45953.4715040279</v>
+        <v>45953.47150402778</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Nitra – Sl</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Nitra – Slovan BratislavaSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>24/10 16:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+147%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45953.53281772471</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -2010,10 +2010,8 @@
           <t>24/10 16:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>175</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45953.53281772471</v>
+        <v>45953.5328177199</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2027,6 +2027,96 @@
         <v>45953.5328177199</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Twk Inn</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HC Twk Innsbruck Die Haie – BolzanoICE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>24/10 17:15</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+192%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45953.59929959945</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Langnau Ti</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Langnau Tigers – LausanneSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>24/10 17:45</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+116%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45953.59929959945</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -2053,10 +2053,8 @@
           <t>24/10 17:15</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>200</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2069,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45953.59929959945</v>
+        <v>45953.59929959491</v>
       </c>
     </row>
     <row r="39">
@@ -2098,10 +2096,8 @@
           <t>24/10 17:45</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>140</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2114,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45953.59929959945</v>
+        <v>45953.59929959491</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2113,6 +2113,141 @@
         <v>45953.59929959491</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Columbus B</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Columbus Blue Jackets – Washington CapitalsNHL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>24/10 23:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+168%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45953.6861821846</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Buffalo Sa</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Buffalo Sabres – Toronto Maple LeafsNHL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>24/10 23:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+167%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45953.6861821846</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | New Jersey</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>New Jersey Devils – San Jose SharksNHL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>24/10 23:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,30%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+161%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45953.6861821846</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,8 @@
           <t>24/10 23:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>200</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45953.6861821846</v>
+        <v>45953.6861821875</v>
       </c>
     </row>
     <row r="41">
@@ -2184,10 +2182,8 @@
           <t>24/10 23:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>200</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2200,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45953.6861821846</v>
+        <v>45953.6861821875</v>
       </c>
     </row>
     <row r="42">
@@ -2229,10 +2225,8 @@
           <t>24/10 23:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>200</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2245,7 +2239,52 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45953.6861821846</v>
+        <v>45953.6861821875</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Wolfsburg </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Wolfsburg Grizzly – Iserlohn RoostersAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>24/10 17:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+134%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45953.72171829672</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -2268,10 +2268,8 @@
           <t>24/10 17:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>175</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2284,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45953.72171829672</v>
+        <v>45953.72171829861</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2285,6 +2285,51 @@
         <v>45953.72171829861</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Wild Wings</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Wild Wings – Nuremberg Ice TigersDEL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>24/10 17:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+118%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45953.84962710593</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,23 +2311,66 @@
           <t>24/10 17:30</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" t="n">
+        <v>150</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+118%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45953.84962710648</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sparta Prague – LitvinovRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>26/10 17:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>150.00</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>+118%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>45953.84962710593</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+115%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45953.88791753051</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2354,10 +2354,8 @@
           <t>26/10 17:30</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>150</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,52 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45953.88791753051</v>
+        <v>45953.88791753472</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Schwenning</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Schwenninger Wild Wings – Nurnberg Ice TigersAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>24/10 17:30</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1,30%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+127%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45953.93076496841</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-23.xlsx
+++ b/data/valuebets_database_2025-10-23.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,10 +2397,8 @@
           <t>24/10 17:30</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>175</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2413,7 +2411,97 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45953.93076496841</v>
+        <v>45953.93076496528</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Eisbären B</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Eisbären Berlin – Augsburger PantherAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>25/10 18:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+156%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45953.97142064577</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Adler Mann</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Adler Mannheim – Cologne HaieDEL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>24/10 17:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+103%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45953.97142064577</v>
       </c>
     </row>
   </sheetData>
